--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="IV SEM - JFS" sheetId="1" r:id="rId1"/>
+    <sheet name="List" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="51">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -87,13 +88,103 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>CLASSES COMBINED (2 STUDENTS)</t>
+  </si>
+  <si>
+    <t>TOP UP ON DAA</t>
+  </si>
+  <si>
+    <t>PAT TOP UP</t>
+  </si>
+  <si>
+    <t>2 PROGRAMS</t>
+  </si>
+  <si>
+    <t>Good Friday</t>
+  </si>
+  <si>
+    <t>Ambedkar Jayanthi</t>
+  </si>
+  <si>
+    <t>3 PROGRAMS</t>
+  </si>
+  <si>
+    <t>Practice on Arrays</t>
+  </si>
+  <si>
+    <t>Leave</t>
+  </si>
+  <si>
+    <t>SB1</t>
+  </si>
+  <si>
+    <t>DisplayBatch.java</t>
+  </si>
+  <si>
+    <t>DisplayBranch.java</t>
+  </si>
+  <si>
+    <t>NumberGame.java</t>
+  </si>
+  <si>
+    <t>MaxNumber.java</t>
+  </si>
+  <si>
+    <t>MinNumber.java</t>
+  </si>
+  <si>
+    <t>LargestNumber.java</t>
+  </si>
+  <si>
+    <t>GFG</t>
+  </si>
+  <si>
+    <t>REG/Lateral CSE</t>
+  </si>
+  <si>
+    <t>SU/SB/SN 1-6</t>
+  </si>
+  <si>
+    <t>Read N elements , disp Max using Arrays</t>
+  </si>
+  <si>
+    <t>Read N elements , disp Min using Arrays</t>
+  </si>
+  <si>
+    <t>JavaOperators.java</t>
+  </si>
+  <si>
+    <t>Collections - AL_AllOps.java</t>
+  </si>
+  <si>
+    <t>Among 4 numbers with out arrays</t>
+  </si>
+  <si>
+    <t>A/U/L/T/A/BS/R/IoOf Operators</t>
+  </si>
+  <si>
+    <t>Basic Operations</t>
+  </si>
+  <si>
+    <t>TOP-UP End</t>
+  </si>
+  <si>
+    <t>510 -aditya java installation</t>
+  </si>
+  <si>
+    <t>BatchSelection.java</t>
+  </si>
+  <si>
+    <t>Either SB1 or SB2 based on Stud Marks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -109,8 +200,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,8 +245,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -185,43 +295,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -234,15 +307,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -253,47 +319,66 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -576,345 +661,1169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.90625" customWidth="1"/>
+    <col min="3" max="3" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="2">
         <v>46090</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
       <c r="G3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="2">
         <v>46091</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="2">
         <v>46092</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="C5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="2">
         <v>46093</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="2">
         <v>46097</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="2">
         <v>46098</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="2">
         <v>46099</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="C12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="2">
         <v>46101</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="21" t="s">
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="2">
         <v>46104</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="2">
         <v>46105</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="2">
         <v>46106</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="21" t="s">
+      <c r="C19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="2">
         <v>46107</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="21" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="21" t="s">
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="2">
         <v>46109</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="21" t="s">
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="21" t="s">
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="2">
         <v>46111</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46116</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46117</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46118</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2">
+        <v>46123</v>
+      </c>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="2">
+        <v>46124</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2">
+        <v>46125</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="2">
+        <v>46130</v>
+      </c>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="2">
+        <v>46131</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46132</v>
+      </c>
+      <c r="C45" s="15"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46137</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46138</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C52" s="15"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C57" s="15"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46145</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C59" s="15"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="16">
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="C58:F58"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C15:F15"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C3:J20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="8.7265625" style="14"/>
+    <col min="4" max="4" width="26.453125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="8.26953125" customWidth="1"/>
+    <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="D3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C4" s="14">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C5" s="14">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C6" s="14">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C7" s="14">
+        <v>4</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="3">
+        <v>4</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C8" s="14">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C9" s="14">
+        <v>6</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="3">
+        <v>6</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C10" s="14">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="H10" s="3">
+        <v>7</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C11" s="14">
+        <v>8</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="H11" s="3">
+        <v>8</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C12" s="14">
+        <v>9</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="H12" s="3">
+        <v>9</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C13" s="14">
+        <v>10</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="H13" s="3">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C14" s="14">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="H14" s="3">
+        <v>11</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C15" s="14">
+        <v>12</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="H15" s="3">
+        <v>12</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C16" s="14">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="H16" s="3">
+        <v>13</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C17" s="14">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="H17" s="3">
+        <v>14</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C18" s="14">
+        <v>15</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="H18" s="3">
+        <v>15</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="H19" s="3">
+        <v>16</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="C20" s="14">
+        <v>17</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="H20" s="3">
+        <v>17</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="IV SEM - JFS" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -135,9 +135,6 @@
     <t>MinNumber.java</t>
   </si>
   <si>
-    <t>LargestNumber.java</t>
-  </si>
-  <si>
     <t>GFG</t>
   </si>
   <si>
@@ -178,6 +175,48 @@
   </si>
   <si>
     <t>Either SB1 or SB2 based on Stud Marks</t>
+  </si>
+  <si>
+    <t>InheritedIntfDemo.java</t>
+  </si>
+  <si>
+    <t>InterfaceDemo.java</t>
+  </si>
+  <si>
+    <t>Basic Arithmetic operations using interface</t>
+  </si>
+  <si>
+    <t>Basic Scientific operations using interfaces</t>
+  </si>
+  <si>
+    <t>2 Interfaces Programs + 2 Assignments</t>
+  </si>
+  <si>
+    <t>LCMGCD.java</t>
+  </si>
+  <si>
+    <t>SICI.java</t>
+  </si>
+  <si>
+    <t>LargestOfFour.java</t>
+  </si>
+  <si>
+    <t>AL_AllOps.java</t>
+  </si>
+  <si>
+    <t>LL_AllOps.java</t>
+  </si>
+  <si>
+    <t>Vector_AllOps.java</t>
+  </si>
+  <si>
+    <t>Stack_AllOps.java</t>
+  </si>
+  <si>
+    <t>ADQ_AllOps.java</t>
+  </si>
+  <si>
+    <t>PQ_AllOps.java</t>
   </si>
 </sst>
 </file>
@@ -208,7 +247,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -254,6 +293,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -307,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -358,6 +403,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -371,15 +428,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -666,20 +714,19 @@
   <cols>
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="33.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -759,12 +806,12 @@
       <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
@@ -776,12 +823,12 @@
       <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -790,12 +837,12 @@
       <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
@@ -844,12 +891,12 @@
       <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
@@ -872,12 +919,12 @@
       <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -886,12 +933,12 @@
       <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -955,12 +1002,12 @@
       <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -981,12 +1028,12 @@
       <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
@@ -1049,12 +1096,12 @@
       <c r="B28" s="2">
         <v>46115</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
@@ -1075,12 +1122,12 @@
       <c r="B30" s="2">
         <v>46117</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
@@ -1108,7 +1155,7 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1130,7 +1177,9 @@
       <c r="B34" s="2">
         <v>46121</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -1143,7 +1192,9 @@
         <v>46122</v>
       </c>
       <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
+      <c r="D35" s="4" t="s">
+        <v>54</v>
+      </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
     </row>
@@ -1166,12 +1217,12 @@
       <c r="B37" s="2">
         <v>46124</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
@@ -1192,12 +1243,12 @@
       <c r="B39" s="2">
         <v>46126</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
@@ -1254,12 +1305,12 @@
       <c r="B44" s="2">
         <v>46131</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
@@ -1340,12 +1391,12 @@
       <c r="B51" s="2">
         <v>46138</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
@@ -1426,12 +1477,12 @@
       <c r="B58" s="2">
         <v>46145</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
@@ -1483,6 +1534,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C58:F58"/>
@@ -1493,12 +1550,6 @@
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1512,12 +1563,12 @@
   <cols>
     <col min="3" max="3" width="8.7265625" style="14"/>
     <col min="4" max="4" width="26.453125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.90625" style="14" customWidth="1"/>
     <col min="7" max="7" width="9.1796875" customWidth="1"/>
     <col min="8" max="8" width="8.26953125" customWidth="1"/>
     <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:10" x14ac:dyDescent="0.35">
@@ -1551,7 +1602,7 @@
         <v>31</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.35">
@@ -1574,7 +1625,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.35">
@@ -1582,7 +1633,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>34</v>
@@ -1597,15 +1648,15 @@
         <v>33</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C7" s="14">
         <v>4</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>48</v>
+      <c r="D7" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>35</v>
@@ -1620,7 +1671,7 @@
         <v>34</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.35">
@@ -1628,10 +1679,10 @@
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>35</v>
@@ -1643,7 +1694,7 @@
         <v>35</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.35">
@@ -1652,19 +1703,19 @@
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H9" s="3">
         <v>6</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.35">
@@ -1672,16 +1723,20 @@
         <v>7</v>
       </c>
       <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="E10" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="H10" s="3">
         <v>7</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.35">
@@ -1689,16 +1744,20 @@
         <v>8</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="E11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="H11" s="3">
         <v>8</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.35">
@@ -1706,16 +1765,20 @@
         <v>9</v>
       </c>
       <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="E12" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="H12" s="3">
         <v>9</v>
       </c>
       <c r="I12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.35">
@@ -1723,13 +1786,21 @@
         <v>10</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="E13" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>56</v>
+      </c>
       <c r="H13" s="3">
         <v>10</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C14" s="14">
@@ -1741,8 +1812,12 @@
       <c r="H14" s="3">
         <v>11</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C15" s="14">
@@ -1754,7 +1829,9 @@
       <c r="H15" s="3">
         <v>12</v>
       </c>
-      <c r="I15" s="4"/>
+      <c r="I15" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.35">
@@ -1767,7 +1844,9 @@
       <c r="H16" s="3">
         <v>13</v>
       </c>
-      <c r="I16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.35">
@@ -1780,7 +1859,9 @@
       <c r="H17" s="3">
         <v>14</v>
       </c>
-      <c r="I17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.35">
@@ -1793,7 +1874,9 @@
       <c r="H18" s="3">
         <v>15</v>
       </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.35">
@@ -1806,7 +1889,9 @@
       <c r="H19" s="3">
         <v>16</v>
       </c>
-      <c r="I19" s="4"/>
+      <c r="I19" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.35">
@@ -1819,7 +1904,9 @@
       <c r="H20" s="3">
         <v>17</v>
       </c>
-      <c r="I20" s="4"/>
+      <c r="I20" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="J20" s="4"/>
     </row>
   </sheetData>

--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -14,6 +14,7 @@
   <sheets>
     <sheet name="IV SEM - JFS" sheetId="1" r:id="rId1"/>
     <sheet name="List" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="116">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -217,6 +218,162 @@
   </si>
   <si>
     <t>PQ_AllOps.java</t>
+  </si>
+  <si>
+    <t>HMap_AllOps.java</t>
+  </si>
+  <si>
+    <t>TMap_AllOps.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List </t>
+  </si>
+  <si>
+    <t>Queue</t>
+  </si>
+  <si>
+    <t>Set</t>
+  </si>
+  <si>
+    <t>LHset_AllOps.java</t>
+  </si>
+  <si>
+    <t>Hset_AllOps.java</t>
+  </si>
+  <si>
+    <t>Tset_AllOps.java</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>AL,V,S,LL</t>
+  </si>
+  <si>
+    <t>ADQ,PQ</t>
+  </si>
+  <si>
+    <t>TS,HS,LHS</t>
+  </si>
+  <si>
+    <t>HM,LHM,HT,TM</t>
+  </si>
+  <si>
+    <t>CBC WORKSHOP</t>
+  </si>
+  <si>
+    <t>GenerateUL.java</t>
+  </si>
+  <si>
+    <t>remove duplicate elements from an ArrayList using function</t>
+  </si>
+  <si>
+    <t>2 programs</t>
+  </si>
+  <si>
+    <t>SU1</t>
+  </si>
+  <si>
+    <t>4 programs</t>
+  </si>
+  <si>
+    <t>SU</t>
+  </si>
+  <si>
+    <t>SlidingWindowMax.java</t>
+  </si>
+  <si>
+    <t>GCDLCMProgram.java</t>
+  </si>
+  <si>
+    <t>Klargest.java</t>
+  </si>
+  <si>
+    <t>ArrayDeque Example</t>
+  </si>
+  <si>
+    <t>PriorityQueue Example</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>S. No.</t>
+  </si>
+  <si>
+    <t>Program Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Collections Basics</t>
+  </si>
+  <si>
+    <t>Interface</t>
+  </si>
+  <si>
+    <t>ArrayList</t>
+  </si>
+  <si>
+    <t>Operators</t>
+  </si>
+  <si>
+    <t>Arrays</t>
+  </si>
+  <si>
+    <t>Random Function</t>
+  </si>
+  <si>
+    <t>String Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Basic Methods </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ArrayDeque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PriorityQueue </t>
+  </si>
+  <si>
+    <t>InterestProgram</t>
+  </si>
+  <si>
+    <t>calculate GCDLCM</t>
+  </si>
+  <si>
+    <t>Kth Smallest Element</t>
+  </si>
+  <si>
+    <t>KthSmallest.java</t>
+  </si>
+  <si>
+    <t>TextEditor.java</t>
+  </si>
+  <si>
+    <t>Stack and Vector</t>
+  </si>
+  <si>
+    <t>undo/redo/history</t>
+  </si>
+  <si>
+    <t>StudentTasks.java</t>
+  </si>
+  <si>
+    <t>LinkedList</t>
+  </si>
+  <si>
+    <t>StudentStack.java</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack </t>
+  </si>
+  <si>
+    <t>StudentManager.java</t>
+  </si>
+  <si>
+    <t>LL,Stack,Vector</t>
   </si>
 </sst>
 </file>
@@ -247,7 +404,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,6 +459,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -352,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -412,9 +593,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -429,6 +611,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,18 +909,20 @@
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="25"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -742,7 +938,9 @@
         <v>18</v>
       </c>
       <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="F2" s="13" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
@@ -806,12 +1004,12 @@
       <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
@@ -823,12 +1021,12 @@
       <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -837,12 +1035,12 @@
       <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
@@ -891,12 +1089,12 @@
       <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
@@ -919,12 +1117,12 @@
       <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -933,12 +1131,12 @@
       <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -1002,12 +1200,12 @@
       <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -1028,12 +1226,12 @@
       <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
@@ -1096,12 +1294,12 @@
       <c r="B28" s="2">
         <v>46115</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
@@ -1122,12 +1320,12 @@
       <c r="B30" s="2">
         <v>46117</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
@@ -1217,12 +1415,12 @@
       <c r="B37" s="2">
         <v>46124</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
@@ -1243,12 +1441,12 @@
       <c r="B39" s="2">
         <v>46126</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
@@ -1259,7 +1457,9 @@
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -1269,7 +1469,9 @@
       <c r="B41" s="2">
         <v>46128</v>
       </c>
-      <c r="C41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -1282,7 +1484,9 @@
         <v>46129</v>
       </c>
       <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="D42" s="4" t="s">
+        <v>80</v>
+      </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
     </row>
@@ -1305,12 +1509,12 @@
       <c r="B44" s="2">
         <v>46131</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
@@ -1334,7 +1538,9 @@
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="F46" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
@@ -1391,12 +1597,12 @@
       <c r="B51" s="2">
         <v>46138</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
@@ -1477,12 +1683,12 @@
       <c r="B58" s="2">
         <v>46145</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
@@ -1534,12 +1740,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C58:F58"/>
@@ -1550,6 +1750,12 @@
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1558,20 +1764,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:J20"/>
+  <dimension ref="C3:P43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="8.7265625" style="14"/>
     <col min="4" max="4" width="26.453125" style="14" customWidth="1"/>
     <col min="5" max="5" width="20.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.90625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" customWidth="1"/>
-    <col min="8" max="8" width="8.26953125" customWidth="1"/>
-    <col min="9" max="9" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.90625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" customWidth="1"/>
+    <col min="9" max="9" width="8.26953125" customWidth="1"/>
+    <col min="10" max="10" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.453125" customWidth="1"/>
+    <col min="16" max="16" width="22.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:16" x14ac:dyDescent="0.35">
       <c r="D3" s="8" t="s">
         <v>30</v>
       </c>
@@ -1581,8 +1790,23 @@
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="G3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C4" s="14">
         <v>1</v>
       </c>
@@ -1595,17 +1819,23 @@
       <c r="F4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3">
+      <c r="G4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="K4" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L4" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C5" s="14">
         <v>2</v>
       </c>
@@ -1618,17 +1848,32 @@
       <c r="F5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="3">
+      <c r="G5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3">
         <v>2</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="N5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5">
+        <v>4</v>
+      </c>
+      <c r="P5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C6" s="14">
         <v>3</v>
       </c>
@@ -1641,17 +1886,32 @@
       <c r="F6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="3">
+      <c r="G6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="3">
         <v>3</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="K6" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6" t="s">
+        <v>67</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="P6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C7" s="14">
         <v>4</v>
       </c>
@@ -1664,17 +1924,32 @@
       <c r="F7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="3">
+      <c r="G7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="3">
         <v>4</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="K7" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C8" s="14">
         <v>5</v>
       </c>
@@ -1687,17 +1962,30 @@
       <c r="F8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="3">
+      <c r="G8" s="7"/>
+      <c r="I8" s="3">
         <v>5</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L8" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C9" s="14">
         <v>6</v>
       </c>
@@ -1708,17 +1996,21 @@
       <c r="F9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="3">
+      <c r="G9" s="7"/>
+      <c r="I9" s="3">
         <v>6</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="J9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L9" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C10" s="14">
         <v>7</v>
       </c>
@@ -1729,17 +2021,24 @@
       <c r="F10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="3">
+      <c r="G10" s="7"/>
+      <c r="I10" s="3">
         <v>7</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L10" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C11" s="14">
         <v>8</v>
       </c>
@@ -1750,17 +2049,21 @@
       <c r="F11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="3">
+      <c r="G11" s="7"/>
+      <c r="I11" s="3">
         <v>8</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L11" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C12" s="14">
         <v>9</v>
       </c>
@@ -1771,17 +2074,21 @@
       <c r="F12" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="3">
+      <c r="G12" s="22"/>
+      <c r="I12" s="3">
         <v>9</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="K12" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L12" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C13" s="14">
         <v>10</v>
       </c>
@@ -1792,125 +2099,450 @@
       <c r="F13" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="H13" s="3">
+      <c r="G13" s="22"/>
+      <c r="I13" s="3">
         <v>10</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L13" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C14" s="14">
         <v>11</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3">
+      <c r="E14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="23"/>
+      <c r="I14" s="3">
         <v>11</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="J14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="K14" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="15" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="L14" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C15" s="14">
         <v>12</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3">
+      <c r="E15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="I15" s="3">
         <v>12</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="K15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L15" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="3:16" x14ac:dyDescent="0.35">
       <c r="C16" s="14">
         <v>13</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-      <c r="H16" s="3">
+      <c r="G16" s="3"/>
+      <c r="I16" s="3">
         <v>13</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="K16" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C17" s="14">
         <v>14</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="H17" s="3">
+      <c r="G17" s="3"/>
+      <c r="I17" s="3">
         <v>14</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="K17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L17" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C18" s="14">
         <v>15</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="H18" s="3">
+      <c r="G18" s="3"/>
+      <c r="I18" s="3">
         <v>15</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="J18" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="K18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C19" s="14">
         <v>16</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="H19" s="3">
+      <c r="G19" s="3"/>
+      <c r="I19" s="3">
         <v>16</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.35">
+      <c r="K19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
       <c r="C20" s="14">
         <v>17</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-      <c r="H20" s="3">
+      <c r="G20" s="3"/>
+      <c r="I20" s="3">
         <v>17</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="J20" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="4"/>
+      <c r="K20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I21" s="3">
+        <v>18</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I22" s="3">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L22" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I23" s="3">
+        <v>20</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L23" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I24" s="3">
+        <v>21</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L24" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I25" s="3">
+        <v>22</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I26" s="3">
+        <v>23</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I27" s="3">
+        <v>24</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I28" s="3">
+        <v>25</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I29" s="3">
+        <v>26</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I30" s="3">
+        <v>27</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I31" s="3">
+        <v>28</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L31" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="I32" s="3">
+        <v>29</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I33" s="3">
+        <v>30</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I34" s="3">
+        <v>31</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I35" s="3">
+        <v>32</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I36" s="3">
+        <v>33</v>
+      </c>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+    </row>
+    <row r="37" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I37" s="3">
+        <v>34</v>
+      </c>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+    </row>
+    <row r="38" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I38" s="3">
+        <v>35</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+    </row>
+    <row r="39" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I39" s="3">
+        <v>36</v>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+    </row>
+    <row r="40" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I40" s="3">
+        <v>37</v>
+      </c>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+    </row>
+    <row r="41" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I41" s="3">
+        <v>38</v>
+      </c>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+    </row>
+    <row r="42" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I42" s="3">
+        <v>39</v>
+      </c>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+    </row>
+    <row r="43" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="I43" s="3">
+        <v>40</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="169">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -169,9 +169,6 @@
     <t>TOP-UP End</t>
   </si>
   <si>
-    <t>510 -aditya java installation</t>
-  </si>
-  <si>
     <t>BatchSelection.java</t>
   </si>
   <si>
@@ -374,13 +371,175 @@
   </si>
   <si>
     <t>LL,Stack,Vector</t>
+  </si>
+  <si>
+    <t>RemoveDuplicatesLast.java</t>
+  </si>
+  <si>
+    <t>Two Equal Sum Subarrays (GFG)</t>
+  </si>
+  <si>
+    <t>sum-of-distances (LC)</t>
+  </si>
+  <si>
+    <t>3 programs</t>
+  </si>
+  <si>
+    <t>HashSet</t>
+  </si>
+  <si>
+    <t>Remove Duplicates and keep last occurance</t>
+  </si>
+  <si>
+    <t>List</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>VECTOR</t>
+  </si>
+  <si>
+    <t>STACK</t>
+  </si>
+  <si>
+    <t>LL</t>
+  </si>
+  <si>
+    <t>AL_Vector.java</t>
+  </si>
+  <si>
+    <t>MultiThreading Concept</t>
+  </si>
+  <si>
+    <t>Vector</t>
+  </si>
+  <si>
+    <t>ADQ</t>
+  </si>
+  <si>
+    <t>PQ</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>HS</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>StudentSystem.java</t>
+  </si>
+  <si>
+    <t>SortLastDig.java</t>
+  </si>
+  <si>
+    <t>TreeSet</t>
+  </si>
+  <si>
+    <t>Registration and sorted</t>
+  </si>
+  <si>
+    <t>sorted using comparator</t>
+  </si>
+  <si>
+    <t>Undo and peek actions</t>
+  </si>
+  <si>
+    <t>First and last adding and removing</t>
+  </si>
+  <si>
+    <t>Both List intended classes</t>
+  </si>
+  <si>
+    <t>HM</t>
+  </si>
+  <si>
+    <t>LHM</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
+    <t>TM</t>
+  </si>
+  <si>
+    <t>HMOrder.java</t>
+  </si>
+  <si>
+    <t>LHMOrder.java</t>
+  </si>
+  <si>
+    <t>not guarantee order</t>
+  </si>
+  <si>
+    <t>guaranteed order (based on insertion)</t>
+  </si>
+  <si>
+    <t>HashMap</t>
+  </si>
+  <si>
+    <t>LinkedHashMap</t>
+  </si>
+  <si>
+    <t>HTOrder.java</t>
+  </si>
+  <si>
+    <t>HashTable</t>
+  </si>
+  <si>
+    <t>TMOrder.java</t>
+  </si>
+  <si>
+    <t>Sorted order</t>
+  </si>
+  <si>
+    <t>TreeMap</t>
+  </si>
+  <si>
+    <t>Null Not allowed</t>
+  </si>
+  <si>
+    <t>EmployeeSystem.java</t>
+  </si>
+  <si>
+    <t>Employee and Department</t>
+  </si>
+  <si>
+    <t>Remove Duplicates but maintain last occurance</t>
+  </si>
+  <si>
+    <t>Find Missing Numbers within the given range</t>
+  </si>
+  <si>
+    <t>Find frequency count of each element in the list</t>
+  </si>
+  <si>
+    <t>Remove consecutive duplicates only</t>
+  </si>
+  <si>
+    <t>Pangram (all alphabets atleast appear once)</t>
+  </si>
+  <si>
+    <t>Threads</t>
+  </si>
+  <si>
+    <t>vector</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>LInkedList</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,15 +555,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +635,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -533,7 +691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -584,9 +742,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -596,7 +751,26 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -611,24 +785,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCC99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -903,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
@@ -915,14 +1082,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -939,7 +1106,7 @@
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
@@ -1004,12 +1171,12 @@
       <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
@@ -1021,12 +1188,12 @@
       <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -1035,12 +1202,12 @@
       <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
@@ -1089,12 +1256,12 @@
       <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
@@ -1117,12 +1284,12 @@
       <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -1131,12 +1298,12 @@
       <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -1200,12 +1367,12 @@
       <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -1226,12 +1393,12 @@
       <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
@@ -1294,12 +1461,12 @@
       <c r="B28" s="2">
         <v>46115</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
@@ -1320,12 +1487,12 @@
       <c r="B30" s="2">
         <v>46117</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
@@ -1376,7 +1543,7 @@
         <v>46121</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -1391,7 +1558,7 @@
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -1415,12 +1582,12 @@
       <c r="B37" s="2">
         <v>46124</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
@@ -1441,12 +1608,12 @@
       <c r="B39" s="2">
         <v>46126</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
@@ -1458,7 +1625,7 @@
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1470,7 +1637,7 @@
         <v>46128</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -1485,7 +1652,7 @@
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -1509,12 +1676,12 @@
       <c r="B44" s="2">
         <v>46131</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
@@ -1539,7 +1706,7 @@
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -1550,7 +1717,6 @@
         <v>46134</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
@@ -1561,7 +1727,9 @@
       <c r="B48" s="2">
         <v>46135</v>
       </c>
-      <c r="C48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -1574,7 +1742,9 @@
         <v>46136</v>
       </c>
       <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
     </row>
@@ -1597,12 +1767,12 @@
       <c r="B51" s="2">
         <v>46138</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
@@ -1683,12 +1853,12 @@
       <c r="B58" s="2">
         <v>46145</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
@@ -1738,8 +1908,26 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
     </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C58:F58"/>
@@ -1750,12 +1938,6 @@
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -1764,23 +1946,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:P43"/>
+  <dimension ref="C3:R43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="8.7265625" style="14"/>
-    <col min="4" max="4" width="26.453125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="20.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.90625" style="14" customWidth="1"/>
+    <col min="4" max="4" width="40.6328125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.54296875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="22.90625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="40.6328125" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.1796875" customWidth="1"/>
     <col min="9" max="9" width="8.26953125" customWidth="1"/>
     <col min="10" max="10" width="23.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="51.26953125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.453125" customWidth="1"/>
-    <col min="16" max="16" width="22.453125" customWidth="1"/>
+    <col min="15" max="15" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.6328125" customWidth="1"/>
+    <col min="17" max="17" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:18" x14ac:dyDescent="0.35">
       <c r="D3" s="8" t="s">
         <v>30</v>
       </c>
@@ -1790,23 +1975,23 @@
       <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="31" t="s">
+      <c r="G3" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="K3" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="L3" s="31" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="L3" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C4" s="14">
         <v>1</v>
       </c>
@@ -1832,10 +2017,10 @@
         <v>38</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C5" s="14">
         <v>2</v>
       </c>
@@ -1861,19 +2046,19 @@
         <v>37</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O5">
         <v>4</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C6" s="14">
         <v>3</v>
       </c>
@@ -1887,7 +2072,7 @@
         <v>33</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I6" s="3">
         <v>3</v>
@@ -1899,23 +2084,23 @@
         <v>36</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O6">
         <v>2</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="3:16" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C7" s="14">
         <v>4</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="7" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -1925,7 +2110,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I7" s="3">
         <v>4</v>
@@ -1937,32 +2122,34 @@
         <v>39</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O7">
         <v>3</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C8" s="14">
         <v>5</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="7" t="s">
+        <v>160</v>
+      </c>
       <c r="I8" s="3">
         <v>5</v>
       </c>
@@ -1973,55 +2160,63 @@
         <v>40</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O8">
         <v>4</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C9" s="14">
         <v>6</v>
       </c>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>166</v>
+      </c>
       <c r="E9" s="7" t="s">
         <v>41</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="7"/>
+        <v>56</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="I9" s="3">
         <v>6</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C10" s="14">
         <v>7</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>167</v>
+      </c>
       <c r="E10" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="7"/>
+        <v>50</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>161</v>
+      </c>
       <c r="I10" s="3">
         <v>7</v>
       </c>
@@ -2032,224 +2227,295 @@
         <v>44</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O10">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="3:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C11" s="14">
         <v>8</v>
       </c>
-      <c r="D11" s="7"/>
+      <c r="D11" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="E11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="7"/>
+        <v>49</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>163</v>
+      </c>
       <c r="I11" s="3">
         <v>8</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="3:16" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C12" s="14">
         <v>9</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="22"/>
+      <c r="D12" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>164</v>
+      </c>
       <c r="I12" s="3">
         <v>9</v>
       </c>
       <c r="J12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="L12" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C13" s="14">
         <v>10</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="22"/>
+      <c r="E13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>50</v>
+      </c>
       <c r="I13" s="3">
         <v>10</v>
       </c>
       <c r="J13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="14" spans="3:16" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C14" s="14">
         <v>11</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="23"/>
+        <v>57</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>49</v>
+      </c>
       <c r="I14" s="3">
         <v>11</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="3:16" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C15" s="14">
         <v>12</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>77</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="21"/>
       <c r="I15" s="3">
         <v>12</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="3:16" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L15" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="P15" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C16" s="14">
         <v>13</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="I16" s="3">
         <v>13</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N16" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="O16" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="P16" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C17" s="14">
         <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
+      <c r="E17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="G17" s="3"/>
       <c r="I17" s="3">
         <v>14</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L17" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C18" s="14">
         <v>15</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="E18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="G18" s="3"/>
       <c r="I18" s="3">
         <v>15</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L18" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L18" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="P18" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C19" s="14">
         <v>16</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="7" t="s">
+        <v>117</v>
+      </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="3">
         <v>16</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L19" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.35">
       <c r="C20" s="14">
         <v>17</v>
       </c>
@@ -2261,276 +2527,436 @@
         <v>17</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L20" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I21" s="3">
         <v>18</v>
       </c>
-      <c r="J21" s="30" t="s">
-        <v>71</v>
+      <c r="J21" s="22" t="s">
+        <v>70</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L21" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="P21" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I22" s="3">
         <v>19</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L22" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N22" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="O22" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="P22" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I23" s="3">
         <v>20</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L23" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L23" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I24" s="3">
         <v>21</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L24" s="24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I25" s="3">
         <v>22</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="L25" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="L25" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="P25" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I26" s="3">
         <v>23</v>
       </c>
       <c r="J26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L26" s="33" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="L26" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="O26" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="P26" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I27" s="3">
         <v>24</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="P27" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I28" s="3">
         <v>25</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="L28" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I29" s="3">
         <v>26</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="L29" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I30" s="3">
         <v>27</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="L30" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="P30" s="28">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="R30" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I31" s="3">
         <v>28</v>
       </c>
       <c r="J31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K31" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.35">
+      <c r="N31" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="O31" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="P31" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.35">
       <c r="I32" s="3">
         <v>29</v>
       </c>
       <c r="J32" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="L32" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="N32" s="27"/>
+      <c r="O32" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="P32" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I33" s="3">
         <v>30</v>
       </c>
       <c r="J33" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="L33" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="N33" s="27"/>
+      <c r="O33" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="P33" s="28">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I34" s="3">
         <v>31</v>
       </c>
       <c r="J34" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="9:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I35" s="3">
         <v>32</v>
       </c>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-    </row>
-    <row r="36" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J35" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="L35" s="25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I36" s="3">
         <v>33</v>
       </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L36" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I37" s="3">
         <v>34</v>
       </c>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="L37" s="4"/>
     </row>
-    <row r="38" spans="9:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I38" s="3">
         <v>35</v>
       </c>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-    </row>
-    <row r="39" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J38" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I39" s="3">
         <v>36</v>
       </c>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-    </row>
-    <row r="40" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L39" s="25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I40" s="3">
         <v>37</v>
       </c>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-    </row>
-    <row r="41" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J40" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L40" s="25" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="41" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I41" s="3">
         <v>38</v>
       </c>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-    </row>
-    <row r="42" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J41" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="K41" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="L41" s="25" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="42" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I42" s="3">
         <v>39</v>
       </c>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-    </row>
-    <row r="43" spans="9:12" x14ac:dyDescent="0.35">
+      <c r="J42" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L42" s="25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="9:17" x14ac:dyDescent="0.35">
       <c r="I43" s="3">
         <v>40</v>
       </c>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="L43" s="25" t="s">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -533,6 +533,33 @@
   </si>
   <si>
     <t>LInkedList</t>
+  </si>
+  <si>
+    <t>Findmin.java</t>
+  </si>
+  <si>
+    <t>Follows Min heap</t>
+  </si>
+  <si>
+    <t>n-1 minimum</t>
+  </si>
+  <si>
+    <t>FindReqMin.java</t>
+  </si>
+  <si>
+    <t>7 programs</t>
+  </si>
+  <si>
+    <t>SB!</t>
+  </si>
+  <si>
+    <t>All Queue and set methods</t>
+  </si>
+  <si>
+    <t>TreeSetTraversal.java</t>
+  </si>
+  <si>
+    <t>forward and reverse traversal</t>
   </si>
 </sst>
 </file>
@@ -642,7 +669,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -687,11 +714,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -765,6 +803,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1082,14 +1121,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -1104,7 +1143,9 @@
       <c r="D2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="13" t="s">
+        <v>174</v>
+      </c>
       <c r="F2" s="13" t="s">
         <v>82</v>
       </c>
@@ -1171,12 +1212,12 @@
       <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
@@ -1188,12 +1229,12 @@
       <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -1202,12 +1243,12 @@
       <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
@@ -1256,12 +1297,12 @@
       <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
@@ -1284,12 +1325,12 @@
       <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -1298,12 +1339,12 @@
       <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -1367,12 +1408,12 @@
       <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -1393,12 +1434,12 @@
       <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
@@ -1461,12 +1502,12 @@
       <c r="B28" s="2">
         <v>46115</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
@@ -1487,12 +1528,12 @@
       <c r="B30" s="2">
         <v>46117</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
@@ -1582,12 +1623,12 @@
       <c r="B37" s="2">
         <v>46124</v>
       </c>
-      <c r="C37" s="30" t="s">
+      <c r="C37" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
@@ -1608,12 +1649,12 @@
       <c r="B39" s="2">
         <v>46126</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
@@ -1676,12 +1717,12 @@
       <c r="B44" s="2">
         <v>46131</v>
       </c>
-      <c r="C44" s="30" t="s">
+      <c r="C44" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
@@ -1767,12 +1808,12 @@
       <c r="B51" s="2">
         <v>46138</v>
       </c>
-      <c r="C51" s="30" t="s">
+      <c r="C51" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
@@ -1796,7 +1837,9 @@
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="F53" s="4" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
@@ -1807,8 +1850,9 @@
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+      <c r="E54" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
@@ -1817,7 +1861,9 @@
       <c r="B55" s="2">
         <v>46142</v>
       </c>
-      <c r="C55" s="4"/>
+      <c r="C55" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -1853,12 +1899,12 @@
       <c r="B58" s="2">
         <v>46145</v>
       </c>
-      <c r="C58" s="30" t="s">
+      <c r="C58" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
@@ -1946,7 +1992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:R43"/>
+  <dimension ref="C3:T46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="8.7265625" style="14"/>
@@ -1963,6 +2009,7 @@
     <col min="16" max="16" width="14.6328125" customWidth="1"/>
     <col min="17" max="17" width="23.6328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="19" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="3:18" x14ac:dyDescent="0.35">
@@ -2420,7 +2467,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C17" s="14">
         <v>14</v>
       </c>
@@ -2457,7 +2504,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C18" s="14">
         <v>15</v>
       </c>
@@ -2492,7 +2539,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C19" s="14">
         <v>16</v>
       </c>
@@ -2515,12 +2562,14 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C20" s="14">
         <v>17</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
+      <c r="E20" s="22" t="s">
+        <v>169</v>
+      </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="3">
@@ -2536,7 +2585,16 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C21" s="14">
+        <v>18</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
       <c r="I21" s="3">
         <v>18</v>
       </c>
@@ -2560,7 +2618,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C22" s="14">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
       <c r="I22" s="3">
         <v>19</v>
       </c>
@@ -2580,7 +2647,7 @@
         <v>130</v>
       </c>
       <c r="P22" s="28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>85</v>
@@ -2588,8 +2655,23 @@
       <c r="R22" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.35">
+      <c r="S22" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="T22" s="30" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="I23" s="3">
         <v>20</v>
       </c>
@@ -2603,7 +2685,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="E24" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="I24" s="3">
         <v>21</v>
       </c>
@@ -2617,7 +2702,10 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.35">
+      <c r="E25" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="I25" s="3">
         <v>22</v>
       </c>
@@ -2640,8 +2728,11 @@
       <c r="Q25" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.35">
+      <c r="R25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I26" s="3">
         <v>23</v>
       </c>
@@ -2667,7 +2758,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I27" s="3">
         <v>24</v>
       </c>
@@ -2691,7 +2782,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I28" s="3">
         <v>25</v>
       </c>
@@ -2705,7 +2796,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I29" s="3">
         <v>26</v>
       </c>
@@ -2719,7 +2810,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I30" s="3">
         <v>27</v>
       </c>
@@ -2746,7 +2837,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I31" s="3">
         <v>28</v>
       </c>
@@ -2772,7 +2863,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:20" x14ac:dyDescent="0.35">
       <c r="I32" s="3">
         <v>29</v>
       </c>
@@ -2956,6 +3047,39 @@
       </c>
       <c r="L43" s="25" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="9:17" x14ac:dyDescent="0.35">
+      <c r="J44" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="K44" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="L44" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="9:17" x14ac:dyDescent="0.35">
+      <c r="J45" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="K45" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="L45" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="9:17" x14ac:dyDescent="0.35">
+      <c r="J46" t="s">
+        <v>176</v>
+      </c>
+      <c r="K46" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="L46" s="25" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/JFS_TRAINING_IN_CDC_2026.xlsx
+++ b/JFS_TRAINING_IN_CDC_2026.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="180">
   <si>
     <t>BATCHES/DATES</t>
   </si>
@@ -560,6 +560,12 @@
   </si>
   <si>
     <t>forward and reverse traversal</t>
+  </si>
+  <si>
+    <t>Vector concept</t>
+  </si>
+  <si>
+    <t>queue operations</t>
   </si>
 </sst>
 </file>
@@ -804,12 +810,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -822,6 +822,12 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1121,14 +1127,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
@@ -1212,12 +1218,12 @@
       <c r="B7" s="2">
         <v>46094</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
       <c r="J7" t="s">
         <v>20</v>
       </c>
@@ -1229,12 +1235,12 @@
       <c r="B8" s="2">
         <v>46095</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
@@ -1243,12 +1249,12 @@
       <c r="B9" s="2">
         <v>46096</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
@@ -1297,12 +1303,12 @@
       <c r="B13" s="2">
         <v>46100</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
@@ -1325,12 +1331,12 @@
       <c r="B15" s="2">
         <v>46102</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -1339,12 +1345,12 @@
       <c r="B16" s="2">
         <v>46103</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
@@ -1408,12 +1414,12 @@
       <c r="B21" s="2">
         <v>46108</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
@@ -1434,12 +1440,12 @@
       <c r="B23" s="2">
         <v>46110</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
@@ -1502,12 +1508,12 @@
       <c r="B28" s="2">
         <v>46115</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
@@ -1528,12 +1534,12 @@
       <c r="B30" s="2">
         <v>46117</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
@@ -1623,12 +1629,12 @@
       <c r="B37" s="2">
         <v>46124</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
@@ -1649,12 +1655,12 @@
       <c r="B39" s="2">
         <v>46126</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
@@ -1717,12 +1723,12 @@
       <c r="B44" s="2">
         <v>46131</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
@@ -1808,12 +1814,12 @@
       <c r="B51" s="2">
         <v>46138</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
@@ -1899,12 +1905,12 @@
       <c r="B58" s="2">
         <v>46145</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C58" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="36"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
@@ -1968,12 +1974,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="C58:F58"/>
@@ -1984,6 +1984,12 @@
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2547,7 +2553,9 @@
       <c r="E19" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="G19" s="3"/>
       <c r="I19" s="3">
         <v>16</v>
@@ -2570,7 +2578,9 @@
       <c r="E20" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>179</v>
+      </c>
       <c r="G20" s="3"/>
       <c r="I20" s="3">
         <v>17</v>
@@ -2593,7 +2603,9 @@
       <c r="E21" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="22" t="s">
+        <v>169</v>
+      </c>
       <c r="G21" s="3"/>
       <c r="I21" s="3">
         <v>18</v>
@@ -2626,7 +2638,9 @@
       <c r="E22" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="7" t="s">
+        <v>172</v>
+      </c>
       <c r="G22" s="3"/>
       <c r="I22" s="3">
         <v>19</v>
